--- a/data/ER-Mate_간호기록_병합완성본_수정본20260607.xlsx
+++ b/data/ER-Mate_간호기록_병합완성본_수정본20260607.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungkwanchoi/NFH_New/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DE7E5B-C21F-0D4D-A6FF-8C18C40202CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42511BA-D641-C04F-B872-30F02161D60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="2280" windowWidth="29400" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="29400" windowHeight="17460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🗂️ 목차" sheetId="1" r:id="rId1"/>
@@ -19,16 +19,28 @@
     <sheet name="📚 업무 가이드" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'🏥 시술 준비'!$A$2:$E$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'🏥 시술 준비'!$A$2:$E$190</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'📋 필수업무 (퇴원·입원·전원)'!$A$2:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📚 업무 가이드'!$A$2:$E$128</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="543">
   <si>
     <t>간호기록</t>
   </si>
@@ -315,30 +327,12 @@
     <t>CT 조영제</t>
   </si>
   <si>
-    <t>조영제 전처치: Avil 다 들어간 후 30min, 스테로이드는 1hr 후 촬영</t>
-  </si>
-  <si>
     <t>전처치 시작 전 CT실 전화해서 투약 시간 확인</t>
   </si>
   <si>
-    <t>15분 후 영상병동뷰어 확인</t>
-  </si>
-  <si>
-    <t>CT angio+3D: TNI 확인 &amp; HR&gt;70 → betaloc 후 30분 f/u</t>
-  </si>
-  <si>
     <t>MRI</t>
   </si>
   <si>
-    <t>Sedation 시: midazolam #1 출발 시 IVS</t>
-  </si>
-  <si>
-    <t>준비물: O2, mask/nasal, ambu, O2 line, fitting mask</t>
-  </si>
-  <si>
-    <t>이송모니터 + 전문/인턴 동반</t>
-  </si>
-  <si>
     <t>Sedation 후 의식/호흡 확인</t>
   </si>
   <si>
@@ -351,21 +345,12 @@
     <t>심도자술 동의서 (봉합기 포함)</t>
   </si>
   <si>
-    <t>CCU vs 병동 확인 — CCU면 입실동의서 추가</t>
-  </si>
-  <si>
-    <t>Skin prep (사타구니) → DPP → Sandbag</t>
-  </si>
-  <si>
     <t>DAPT 로딩: Aspirin Protect 100mg 3T + Pidogul(Clopidogrel) 75mg 8T + Statin(Lipitor or Vivacor) + 위장약(PPI) — 4가지 P.O 확인</t>
   </si>
   <si>
     <t>기존에 Aspirin이나 clopidogrel 복용하던 사람은 각각 1tab만 복용(주치의확인 추천)</t>
   </si>
   <si>
-    <t>위급상황 아니면 S-CAR로 바꿔서 이송</t>
-  </si>
-  <si>
     <t>BAE</t>
   </si>
   <si>
@@ -408,9 +393,6 @@
     <t>2주 1번 bile bag change</t>
   </si>
   <si>
-    <t>검체 → culture 주치의 noti</t>
-  </si>
-  <si>
     <t>얇은 코니칼튜브</t>
   </si>
   <si>
@@ -423,9 +405,6 @@
     <t>복부경피배액술 동의서</t>
   </si>
   <si>
-    <t>검체 btl → culture 나가는지 주치의 noti</t>
-  </si>
-  <si>
     <t>chestPCD</t>
   </si>
   <si>
@@ -438,9 +417,6 @@
     <t>Chest bottle 걸이, 투약실에 네임라벨 붙이기</t>
   </si>
   <si>
-    <t>혈조 요청시 chest bottle 뜯지말고 보내기</t>
-  </si>
-  <si>
     <t>PCN</t>
   </si>
   <si>
@@ -474,9 +450,6 @@
     <t>뇌파검사</t>
   </si>
   <si>
-    <t>정규: 우리가 예약 / 비정규: 1588-5700 안내</t>
-  </si>
-  <si>
     <t>Echo</t>
   </si>
   <si>
@@ -486,12 +459,6 @@
     <t>TTE면 동의서 필요없음</t>
   </si>
   <si>
-    <t>TEE면 경식도초음파 동의서</t>
-  </si>
-  <si>
-    <t>주치의가 직접 예약 / 인턴도 가능</t>
-  </si>
-  <si>
     <t>DJstent</t>
   </si>
   <si>
@@ -549,9 +516,6 @@
     <t>상의 속옷 탈의</t>
   </si>
   <si>
-    <t>Change/revision 시 연결 수액 모두 제거</t>
-  </si>
-  <si>
     <t>삽입부위 oozing/bleeding 관찰 (필요시 sandbag 압박)</t>
   </si>
   <si>
@@ -561,9 +525,6 @@
     <t>채혈 가능 여부 주치의 확인</t>
   </si>
   <si>
-    <t>혈관조영실 외 삽입 시 Post CPA 오더 필요</t>
-  </si>
-  <si>
     <t>투석용 IJC: 투석/혈장교환 외 사용 금기 (응급 제외)</t>
   </si>
   <si>
@@ -615,12 +576,6 @@
     <t>NPO 8시간</t>
   </si>
   <si>
-    <t>3way 2개 카테터 가까이 IV 확보</t>
-  </si>
-  <si>
-    <t>Etomidate prep, 향정이니 잔량 확인!</t>
-  </si>
-  <si>
     <t>Post 12-lead ECG 촬영, EKG monitoring 유지</t>
   </si>
   <si>
@@ -714,15 +669,9 @@
     <t>Foley 삽입 여부 주치의 확인</t>
   </si>
   <si>
-    <t>수술동의서 확인 — 수술/마취동의서는 해당과에서 받음, ER에서는 수혈동의서까지만</t>
-  </si>
-  <si>
     <t>수술 전 Antibiotics 투여 시간 확인</t>
   </si>
   <si>
-    <t>⚠️ S-car에 눕혀서 이송</t>
-  </si>
-  <si>
     <t>⚠️ 병동인계 후 이송보낸 시간에 이름빼기</t>
   </si>
   <si>
@@ -756,12 +705,6 @@
     <t>요추천자(Lumbar Puncture)</t>
   </si>
   <si>
-    <t>bedside시 성인 척추 천자 동의서, 시술실이면 영상유도하 척추천자 동의서</t>
-  </si>
-  <si>
-    <t>자리 받기</t>
-  </si>
-  <si>
     <t>천자 전 BST check</t>
   </si>
   <si>
@@ -1629,10 +1572,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>20G 이상 손목 위 Pressure line IV</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>혈관조영실 (☏)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1670,6 +1609,196 @@
   </si>
   <si>
     <t>심전도검사실 (☏)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>▶  사망 처리  (12개 항목)</t>
+  </si>
+  <si>
+    <t>사망</t>
+  </si>
+  <si>
+    <t>주치의 사망 선언 확인</t>
+  </si>
+  <si>
+    <t>주치의에게 사망 선언 시각 확인 및 기록</t>
+  </si>
+  <si>
+    <t>사망 시각 기록</t>
+  </si>
+  <si>
+    <t>보호자 연락</t>
+  </si>
+  <si>
+    <t>보호자에게 사망 사실 통보 및 병원 내원 안내</t>
+  </si>
+  <si>
+    <t>시신 정리</t>
+  </si>
+  <si>
+    <t>눈·입 닫기, 자세 정리, 깨끗한 시트로 교체</t>
+  </si>
+  <si>
+    <t>IV line·foley·NG tube 등 의료기기 전부 제거</t>
+  </si>
+  <si>
+    <t>귀중품 확인 및 인계</t>
+  </si>
+  <si>
+    <t>귀중품 목록 작성 후 보호자에게 직접 인계</t>
+  </si>
+  <si>
+    <t>사망진단서 확인</t>
+  </si>
+  <si>
+    <t>사망간호기록지 작성</t>
+  </si>
+  <si>
+    <t>응급실 퇴실 간호기록</t>
+  </si>
+  <si>
+    <t>퇴실 기록에 '사망' 시각 및 사유 입력</t>
+  </si>
+  <si>
+    <t>원무과 사망 신고</t>
+  </si>
+  <si>
+    <t>원무과에 사망 신고 후 행정 처리 확인</t>
+  </si>
+  <si>
+    <t>영안실 연락 및 이송</t>
+  </si>
+  <si>
+    <t>영안실(☏ 내선 확인) 연락 → 이송 등록 후 이송</t>
+  </si>
+  <si>
+    <t>침상 정리 및 소독</t>
+  </si>
+  <si>
+    <t>차트에 정확한 사망 시각 기록(사망시간 = 주치의 사망선언시간 = ECG flat 시간)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>주치의 사망진단서 발급 여부 확인(가족관계증명서 발급 여부 확인 ) 보통 10부</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>사망 전 처치 발행·V/S·경과 포함하여 간호기록 작성</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>간호조무사, 침상·장비 소독 및 정리</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CT동의서 준비(조영제 사용시)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CT Heart angio+3D: TNI 확인 &amp; HR&gt;70 → betaloc 후 30분 f/u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>15분 후 영상병동뷰어 영상 올라왔는지 확인</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GFR 60 이상 확인.(60미만일 시 주치의 확인 필요)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>20G 이상 손목 위 Pressure line IV (Non-Contrast)는 필요없음)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MRI 동의서 준비(조영제 사용시)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sedation 시: midazolam #1 출발 시 IVS 준비물: O2, mask/nasal, ambu, O2 line, fitting mask</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sedation tl 이송모니터 + 의료진 동반</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금속물질(안경, 보청기, 틀니, ECG lead, SPO2 sensor, 뇌심부자극기, pacemaker 등) 제거된 지 직접 확인 및 질문.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICU vs 병동 확인 — ICU면 입실동의서 추가</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>위급상황 아니면 이송용카로 바꿔서 이송</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skin prep (사타구니) → 족배동맥 촉지 확인, 마커 표시, 간호기록 → Sandbag</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>검체 → culture 검사 나갈지 주치의 noti</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEE면 경식도초음파 동의서 + 금식 8시간</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Change/revision 시 Central line 에 연결 된 모든 수액 약물 제거</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>혈관조영실 외 삽입 시 Post Chest xray 오더 필요</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3way 2개 카테터 Antecubital area에 가깝게 IV 확보</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etomidate prep, 향정 투약시 반납 잔량 확인!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술동의서 확인 — 수술/마취동의서 수혈동의서 누가 받을지 확이 후 받기.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Apple Color Emoji"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 이송용 car에 눕혀서 이송</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>bedside시 성인 척추 천자 동의서, 혈관조영실 이면 영상유도하 척추천자 동의서</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>환의(아래 속옷만 입힌다)로 갈아입기 + 귀금속(귀걸이 목걸이 등) 제거 - 영상 방해될 수 있음</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>조영제 알러지 시 전처치: Avil 다 들어간 후 30min, 스테로이드는 1hr 후 촬영</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1677,7 +1806,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1826,8 +1955,21 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <name val="Apple Color Emoji"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1904,8 +2046,23 @@
         <fgColor rgb="FFF3E5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6B4E71"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F0F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1976,11 +2133,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D5DD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2048,10 +2257,10 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2072,19 +2281,48 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2397,18 +2635,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="20" customHeight="1">
       <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="8" customHeight="1"/>
     <row r="4" spans="1:3" ht="22" customHeight="1">
@@ -2459,8 +2697,8 @@
       <c r="A9" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2475,7 +2713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2489,10 +2727,10 @@
       <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="22" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2531,7 +2769,7 @@
         <v>27</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="E4" s="7"/>
     </row>
@@ -2546,7 +2784,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="E5" s="7"/>
     </row>
@@ -2561,7 +2799,7 @@
         <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="E6" s="7"/>
     </row>
@@ -2573,10 +2811,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="E7" s="7"/>
     </row>
@@ -2588,10 +2826,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="E8" s="7"/>
     </row>
@@ -2651,7 +2889,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="E12" s="7"/>
     </row>
@@ -2675,7 +2913,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="E14" s="7"/>
     </row>
@@ -2690,7 +2928,7 @@
         <v>41</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="E15" s="7"/>
     </row>
@@ -2705,7 +2943,7 @@
         <v>42</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="E16" s="7"/>
     </row>
@@ -2720,7 +2958,7 @@
         <v>43</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="E17" s="7"/>
     </row>
@@ -2735,7 +2973,7 @@
         <v>44</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="E18" s="7"/>
     </row>
@@ -2750,7 +2988,7 @@
         <v>45</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="E19" s="7"/>
     </row>
@@ -2765,7 +3003,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="E20" s="7"/>
     </row>
@@ -2777,10 +3015,10 @@
         <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="E21" s="7"/>
     </row>
@@ -2795,7 +3033,7 @@
         <v>37</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="E22" s="7"/>
     </row>
@@ -2819,7 +3057,7 @@
         <v>48</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="E24" s="7"/>
     </row>
@@ -2834,7 +3072,7 @@
         <v>49</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="E25" s="7"/>
     </row>
@@ -2849,7 +3087,7 @@
         <v>50</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="E26" s="7"/>
     </row>
@@ -2864,7 +3102,7 @@
         <v>51</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="E27" s="7"/>
     </row>
@@ -2909,7 +3147,7 @@
         <v>55</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="E30" s="7"/>
     </row>
@@ -2939,7 +3177,7 @@
         <v>59</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="E32" s="7"/>
     </row>
@@ -2954,7 +3192,7 @@
         <v>56</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="E33" s="7"/>
     </row>
@@ -2969,7 +3207,7 @@
         <v>35</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="E34" s="7"/>
     </row>
@@ -2984,17 +3222,207 @@
         <v>37</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="39" t="s">
+        <v>495</v>
+      </c>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="41"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="B37" s="42">
+        <v>1</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>497</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>498</v>
+      </c>
+      <c r="E37" s="42"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="B38" s="43">
+        <v>2</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>499</v>
+      </c>
+      <c r="D38" s="43" t="s">
+        <v>516</v>
+      </c>
+      <c r="E38" s="43"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="B39" s="42">
+        <v>3</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>500</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="E39" s="42"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="B40" s="43">
+        <v>4</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>502</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>503</v>
+      </c>
+      <c r="E40" s="43"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="B41" s="42">
+        <v>5</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="42" t="s">
+        <v>504</v>
+      </c>
+      <c r="E41" s="42"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="B42" s="43">
+        <v>6</v>
+      </c>
+      <c r="C42" s="43" t="s">
+        <v>505</v>
+      </c>
+      <c r="D42" s="43" t="s">
+        <v>506</v>
+      </c>
+      <c r="E42" s="43"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="B43" s="42">
+        <v>7</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>507</v>
+      </c>
+      <c r="D43" s="42" t="s">
+        <v>517</v>
+      </c>
+      <c r="E43" s="42"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="B44" s="43">
+        <v>8</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>508</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>518</v>
+      </c>
+      <c r="E44" s="43"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="B45" s="42">
+        <v>9</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>509</v>
+      </c>
+      <c r="D45" s="42" t="s">
+        <v>510</v>
+      </c>
+      <c r="E45" s="42"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="B46" s="43">
+        <v>10</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>511</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>512</v>
+      </c>
+      <c r="E46" s="43"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="B47" s="42">
+        <v>11</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="D47" s="42" t="s">
+        <v>514</v>
+      </c>
+      <c r="E47" s="42"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="B48" s="43">
+        <v>12</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>515</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>519</v>
+      </c>
+      <c r="E48" s="43"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:E35" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A36:E36"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3003,7 +3431,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3017,10 +3445,10 @@
       <c r="A1" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="22" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -3040,10 +3468,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
-      <c r="A3" s="33" t="s">
-        <v>502</v>
-      </c>
-      <c r="B3" s="36" t="s">
+      <c r="A3" s="36" t="s">
+        <v>479</v>
+      </c>
+      <c r="B3" s="33" t="s">
         <v>64</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -3160,15 +3588,15 @@
         <v>78</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1">
-      <c r="A14" s="33" t="s">
-        <v>503</v>
-      </c>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="36" t="s">
+        <v>480</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="11" t="s">
@@ -3241,15 +3669,15 @@
         <v>78</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
-      <c r="A21" s="33" t="s">
-        <v>505</v>
-      </c>
-      <c r="B21" s="36" t="s">
+      <c r="A21" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>86</v>
       </c>
       <c r="C21" s="11" t="s">
@@ -3311,15 +3739,15 @@
         <v>78</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="E26" s="13"/>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="33" t="s">
         <v>91</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -3370,162 +3798,158 @@
         <v>78</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="E31" s="13"/>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1">
-      <c r="A32" s="33" t="s">
-        <v>506</v>
-      </c>
-      <c r="B32" s="36" t="s">
+      <c r="A32" s="36" t="s">
+        <v>483</v>
+      </c>
+      <c r="B32" s="33" t="s">
         <v>94</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E32" s="13"/>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="34"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="45"/>
       <c r="C33" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>95</v>
+      <c r="D33" s="12" t="s">
+        <v>541</v>
       </c>
       <c r="E33" s="13"/>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="45"/>
       <c r="C34" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>96</v>
+        <v>523</v>
       </c>
       <c r="E34" s="13"/>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>97</v>
+      <c r="A35" s="44"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>524</v>
       </c>
       <c r="E35" s="13"/>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1">
       <c r="A36" s="34"/>
       <c r="B36" s="34"/>
-      <c r="C36" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>98</v>
+      <c r="C36" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>542</v>
       </c>
       <c r="E36" s="13"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1">
-      <c r="A37" s="35"/>
-      <c r="B37" s="35"/>
-      <c r="C37" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>504</v>
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="E37" s="13"/>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1">
-      <c r="A38" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>508</v>
+      <c r="A38" s="34"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>522</v>
       </c>
       <c r="E38" s="13"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1">
       <c r="A39" s="34"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>100</v>
+      <c r="C39" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>521</v>
       </c>
       <c r="E39" s="13"/>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>101</v>
+      <c r="A40" s="35"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>481</v>
       </c>
       <c r="E40" s="13"/>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
+      <c r="A41" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>96</v>
+      </c>
       <c r="C41" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D41" s="14" t="s">
-        <v>102</v>
+      <c r="D41" s="12" t="s">
+        <v>525</v>
       </c>
       <c r="E41" s="13"/>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1">
-      <c r="A42" s="34"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="16" t="s">
-        <v>73</v>
+      <c r="A42" s="44"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>103</v>
+        <v>524</v>
       </c>
       <c r="E42" s="13"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1">
-      <c r="A43" s="35"/>
-      <c r="B43" s="35"/>
-      <c r="C43" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>507</v>
+      <c r="A43" s="44"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>523</v>
       </c>
       <c r="E43" s="13"/>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1">
-      <c r="A44" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="36" t="s">
-        <v>105</v>
-      </c>
+      <c r="A44" s="44"/>
+      <c r="B44" s="45"/>
       <c r="C44" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>106</v>
+        <v>528</v>
       </c>
       <c r="E44" s="13"/>
     </row>
@@ -3536,7 +3960,7 @@
         <v>65</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>107</v>
+        <v>526</v>
       </c>
       <c r="E45" s="13"/>
     </row>
@@ -3546,137 +3970,137 @@
       <c r="C46" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>108</v>
+      <c r="D46" s="14" t="s">
+        <v>527</v>
       </c>
       <c r="E46" s="13"/>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1">
       <c r="A47" s="34"/>
       <c r="B47" s="34"/>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47" s="13"/>
+    </row>
+    <row r="48" spans="1:5" ht="18" customHeight="1">
+      <c r="A48" s="35"/>
+      <c r="B48" s="35"/>
+      <c r="C48" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>484</v>
+      </c>
+      <c r="E48" s="13"/>
+    </row>
+    <row r="49" spans="1:5" ht="18" customHeight="1">
+      <c r="A49" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E49" s="13"/>
+    </row>
+    <row r="50" spans="1:5" ht="18" customHeight="1">
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>529</v>
+      </c>
+      <c r="E50" s="13"/>
+    </row>
+    <row r="51" spans="1:5" ht="18" customHeight="1">
+      <c r="A51" s="44"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="E51" s="13"/>
+    </row>
+    <row r="52" spans="1:5" ht="18" customHeight="1">
+      <c r="A52" s="44"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D47" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E47" s="13"/>
-    </row>
-    <row r="48" spans="1:5" ht="18" customHeight="1">
-      <c r="A48" s="34"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="15" t="s">
+      <c r="D52" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E52" s="13"/>
+    </row>
+    <row r="53" spans="1:5" ht="18" customHeight="1">
+      <c r="A53" s="44"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D48" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E48" s="13"/>
-    </row>
-    <row r="49" spans="1:5" ht="18" customHeight="1">
-      <c r="A49" s="34"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="18" t="s">
+      <c r="D53" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="13"/>
+    </row>
+    <row r="54" spans="1:5" ht="18" customHeight="1">
+      <c r="A54" s="44"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="E49" s="13"/>
-    </row>
-    <row r="50" spans="1:5" ht="18" customHeight="1">
-      <c r="A50" s="35"/>
-      <c r="B50" s="35"/>
-      <c r="C50" s="18" t="s">
+      <c r="D54" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="E54" s="13"/>
+    </row>
+    <row r="55" spans="1:5" ht="18" customHeight="1">
+      <c r="A55" s="49"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="E50" s="13"/>
-    </row>
-    <row r="51" spans="1:5" ht="18" customHeight="1">
-      <c r="A51" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="B51" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="13"/>
-    </row>
-    <row r="52" spans="1:5" ht="18" customHeight="1">
-      <c r="A52" s="34"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E52" s="13"/>
-    </row>
-    <row r="53" spans="1:5" ht="18" customHeight="1">
-      <c r="A53" s="34"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E53" s="13"/>
-    </row>
-    <row r="54" spans="1:5" ht="18" customHeight="1">
-      <c r="A54" s="34"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E54" s="13"/>
-    </row>
-    <row r="55" spans="1:5" ht="18" customHeight="1">
-      <c r="A55" s="34"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="16" t="s">
-        <v>73</v>
-      </c>
       <c r="D55" s="12" t="s">
-        <v>117</v>
+        <v>530</v>
       </c>
       <c r="E55" s="13"/>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1">
-      <c r="A56" s="35"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>509</v>
+      <c r="A56" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="E56" s="13"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1">
-      <c r="A57" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="B57" s="36" t="s">
-        <v>119</v>
-      </c>
+      <c r="A57" s="34"/>
+      <c r="B57" s="34"/>
       <c r="C57" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>120</v>
+        <v>531</v>
       </c>
       <c r="E57" s="13"/>
     </row>
@@ -3686,19 +4110,19 @@
       <c r="C58" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D58" s="14" t="s">
-        <v>108</v>
+      <c r="D58" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="E58" s="13"/>
     </row>
     <row r="59" spans="1:5" ht="18" customHeight="1">
       <c r="A59" s="34"/>
       <c r="B59" s="34"/>
-      <c r="C59" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>115</v>
+      <c r="C59" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="E59" s="13"/>
     </row>
@@ -3708,56 +4132,56 @@
       <c r="C60" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D60" s="14" t="s">
-        <v>116</v>
+      <c r="D60" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="E60" s="13"/>
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1">
-      <c r="A61" s="34"/>
-      <c r="B61" s="34"/>
-      <c r="C61" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>117</v>
+      <c r="A61" s="35"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>485</v>
       </c>
       <c r="E61" s="13"/>
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1">
-      <c r="A62" s="35"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>509</v>
+      <c r="A62" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="E62" s="13"/>
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1">
-      <c r="A63" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="B63" s="36" t="s">
-        <v>122</v>
-      </c>
+      <c r="A63" s="34"/>
+      <c r="B63" s="34"/>
       <c r="C63" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>123</v>
+        <v>531</v>
       </c>
       <c r="E63" s="13"/>
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1">
       <c r="A64" s="34"/>
       <c r="B64" s="34"/>
-      <c r="C64" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>124</v>
+      <c r="C64" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="E64" s="13"/>
     </row>
@@ -3767,8 +4191,8 @@
       <c r="C65" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D65" s="12" t="s">
-        <v>125</v>
+      <c r="D65" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="E65" s="13"/>
     </row>
@@ -3778,45 +4202,45 @@
       <c r="C66" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D66" s="14" t="s">
-        <v>126</v>
+      <c r="D66" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="E66" s="13"/>
     </row>
     <row r="67" spans="1:5" ht="18" customHeight="1">
-      <c r="A67" s="34"/>
-      <c r="B67" s="34"/>
-      <c r="C67" s="16" t="s">
+      <c r="A67" s="35"/>
+      <c r="B67" s="35"/>
+      <c r="C67" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="E67" s="13"/>
+    </row>
+    <row r="68" spans="1:5" ht="18" customHeight="1">
+      <c r="A68" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="13"/>
+    </row>
+    <row r="69" spans="1:5" ht="18" customHeight="1">
+      <c r="A69" s="34"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>517</v>
-      </c>
-      <c r="E67" s="13"/>
-    </row>
-    <row r="68" spans="1:5" ht="18" customHeight="1">
-      <c r="A68" s="35"/>
-      <c r="B68" s="35"/>
-      <c r="C68" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="E68" s="13"/>
-    </row>
-    <row r="69" spans="1:5" ht="18" customHeight="1">
-      <c r="A69" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="B69" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>130</v>
+      <c r="D69" s="14" t="s">
+        <v>115</v>
       </c>
       <c r="E69" s="13"/>
     </row>
@@ -3826,8 +4250,8 @@
       <c r="C70" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D70" s="14" t="s">
-        <v>131</v>
+      <c r="D70" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="E70" s="13"/>
     </row>
@@ -3837,227 +4261,225 @@
       <c r="C71" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D71" s="12" t="s">
-        <v>127</v>
+      <c r="D71" s="14" t="s">
+        <v>532</v>
       </c>
       <c r="E71" s="13"/>
     </row>
     <row r="72" spans="1:5" ht="18" customHeight="1">
-      <c r="A72" s="35"/>
-      <c r="B72" s="35"/>
-      <c r="C72" s="18" t="s">
+      <c r="A72" s="34"/>
+      <c r="B72" s="34"/>
+      <c r="C72" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="E72" s="13"/>
+    </row>
+    <row r="73" spans="1:5" ht="18" customHeight="1">
+      <c r="A73" s="35"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D72" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="E72" s="13"/>
-    </row>
-    <row r="73" spans="1:5" ht="18" customHeight="1">
-      <c r="A73" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="B73" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>134</v>
+      <c r="D73" s="14" t="s">
+        <v>485</v>
       </c>
       <c r="E73" s="13"/>
     </row>
     <row r="74" spans="1:5" ht="18" customHeight="1">
-      <c r="A74" s="34"/>
-      <c r="B74" s="34"/>
+      <c r="A74" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="B74" s="33" t="s">
+        <v>119</v>
+      </c>
       <c r="C74" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D74" s="14" t="s">
-        <v>135</v>
+      <c r="D74" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="E74" s="13"/>
     </row>
     <row r="75" spans="1:5" ht="18" customHeight="1">
       <c r="A75" s="34"/>
       <c r="B75" s="34"/>
-      <c r="C75" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>136</v>
+      <c r="C75" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>532</v>
       </c>
       <c r="E75" s="13"/>
     </row>
     <row r="76" spans="1:5" ht="18" customHeight="1">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="18" t="s">
+      <c r="A76" s="34"/>
+      <c r="B76" s="34"/>
+      <c r="C76" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E76" s="13"/>
+    </row>
+    <row r="77" spans="1:5" ht="18" customHeight="1">
+      <c r="A77" s="35"/>
+      <c r="B77" s="35"/>
+      <c r="C77" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D76" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="E76" s="13"/>
-    </row>
-    <row r="77" spans="1:5" ht="18" customHeight="1">
-      <c r="A77" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="B77" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>139</v>
+      <c r="D77" s="14" t="s">
+        <v>485</v>
       </c>
       <c r="E77" s="13"/>
     </row>
     <row r="78" spans="1:5" ht="18" customHeight="1">
-      <c r="A78" s="34"/>
-      <c r="B78" s="34"/>
+      <c r="A78" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="B78" s="33" t="s">
+        <v>122</v>
+      </c>
       <c r="C78" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D78" s="14" t="s">
-        <v>140</v>
+      <c r="D78" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="E78" s="13"/>
     </row>
     <row r="79" spans="1:5" ht="18" customHeight="1">
       <c r="A79" s="34"/>
       <c r="B79" s="34"/>
-      <c r="C79" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>141</v>
+      <c r="C79" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="E79" s="13"/>
     </row>
     <row r="80" spans="1:5" ht="18" customHeight="1">
-      <c r="A80" s="34"/>
-      <c r="B80" s="34"/>
-      <c r="C80" s="16" t="s">
-        <v>73</v>
+      <c r="A80" s="35"/>
+      <c r="B80" s="35"/>
+      <c r="C80" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>124</v>
+        <v>485</v>
       </c>
       <c r="E80" s="13"/>
     </row>
     <row r="81" spans="1:5" ht="18" customHeight="1">
-      <c r="A81" s="35"/>
-      <c r="B81" s="35"/>
-      <c r="C81" s="18" t="s">
-        <v>78</v>
+      <c r="A81" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>509</v>
+        <v>127</v>
       </c>
       <c r="E81" s="13"/>
     </row>
     <row r="82" spans="1:5" ht="18" customHeight="1">
-      <c r="A82" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="B82" s="36" t="s">
-        <v>143</v>
-      </c>
+      <c r="A82" s="34"/>
+      <c r="B82" s="34"/>
       <c r="C82" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D82" s="12" t="s">
-        <v>144</v>
+      <c r="D82" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E82" s="13"/>
     </row>
     <row r="83" spans="1:5" ht="18" customHeight="1">
       <c r="A83" s="34"/>
       <c r="B83" s="34"/>
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E83" s="13"/>
+    </row>
+    <row r="84" spans="1:5" ht="18" customHeight="1">
+      <c r="A84" s="34"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E84" s="13"/>
+    </row>
+    <row r="85" spans="1:5" ht="18" customHeight="1">
+      <c r="A85" s="35"/>
+      <c r="B85" s="35"/>
+      <c r="C85" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="E85" s="13"/>
+    </row>
+    <row r="86" spans="1:5" ht="18" customHeight="1">
+      <c r="A86" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E86" s="13"/>
+    </row>
+    <row r="87" spans="1:5" ht="18" customHeight="1">
+      <c r="A87" s="34"/>
+      <c r="B87" s="34"/>
+      <c r="C87" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D83" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E83" s="13"/>
-    </row>
-    <row r="84" spans="1:5" ht="18" customHeight="1">
-      <c r="A84" s="35"/>
-      <c r="B84" s="35"/>
-      <c r="C84" s="18" t="s">
+      <c r="D87" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E87" s="13"/>
+    </row>
+    <row r="88" spans="1:5" ht="18" customHeight="1">
+      <c r="A88" s="35"/>
+      <c r="B88" s="35"/>
+      <c r="C88" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D84" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="E84" s="13"/>
-    </row>
-    <row r="85" spans="1:5" ht="18" customHeight="1">
-      <c r="A85" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="B85" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="C85" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E85" s="13"/>
-    </row>
-    <row r="86" spans="1:5" ht="18" customHeight="1">
-      <c r="A86" s="35"/>
-      <c r="B86" s="35"/>
-      <c r="C86" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>510</v>
-      </c>
-      <c r="E86" s="13"/>
-    </row>
-    <row r="87" spans="1:5" ht="18" customHeight="1">
-      <c r="A87" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="B87" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E87" s="13"/>
-    </row>
-    <row r="88" spans="1:5" ht="18" customHeight="1">
-      <c r="A88" s="34"/>
-      <c r="B88" s="34"/>
-      <c r="C88" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D88" s="14" t="s">
-        <v>152</v>
+      <c r="D88" s="12" t="s">
+        <v>494</v>
       </c>
       <c r="E88" s="13"/>
     </row>
     <row r="89" spans="1:5" ht="18" customHeight="1">
-      <c r="A89" s="34"/>
-      <c r="B89" s="34"/>
+      <c r="A89" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B89" s="33" t="s">
+        <v>135</v>
+      </c>
       <c r="C89" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D89" s="12" t="s">
-        <v>153</v>
-      </c>
+      <c r="D89" s="12"/>
       <c r="E89" s="13"/>
     </row>
     <row r="90" spans="1:5" ht="18" customHeight="1">
@@ -4067,22 +4489,22 @@
         <v>78</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="E90" s="13"/>
     </row>
     <row r="91" spans="1:5" ht="18" customHeight="1">
-      <c r="A91" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="B91" s="36" t="s">
-        <v>155</v>
+      <c r="A91" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B91" s="33" t="s">
+        <v>137</v>
       </c>
       <c r="C91" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="E91" s="13"/>
     </row>
@@ -4093,165 +4515,167 @@
         <v>65</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>157</v>
+        <v>533</v>
       </c>
       <c r="E92" s="13"/>
     </row>
     <row r="93" spans="1:5" ht="18" customHeight="1">
       <c r="A93" s="34"/>
       <c r="B93" s="34"/>
-      <c r="C93" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>158</v>
-      </c>
+      <c r="C93" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="12"/>
       <c r="E93" s="13"/>
     </row>
     <row r="94" spans="1:5" ht="18" customHeight="1">
-      <c r="A94" s="34"/>
-      <c r="B94" s="34"/>
-      <c r="C94" s="11" t="s">
-        <v>65</v>
+      <c r="A94" s="35"/>
+      <c r="B94" s="35"/>
+      <c r="C94" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>159</v>
+        <v>487</v>
       </c>
       <c r="E94" s="13"/>
     </row>
     <row r="95" spans="1:5" ht="18" customHeight="1">
-      <c r="A95" s="34"/>
-      <c r="B95" s="34"/>
+      <c r="A95" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" s="33" t="s">
+        <v>140</v>
+      </c>
       <c r="C95" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E95" s="13"/>
     </row>
     <row r="96" spans="1:5" ht="18" customHeight="1">
       <c r="A96" s="34"/>
       <c r="B96" s="34"/>
-      <c r="C96" s="16" t="s">
-        <v>73</v>
+      <c r="C96" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E96" s="13"/>
     </row>
     <row r="97" spans="1:5" ht="18" customHeight="1">
       <c r="A97" s="34"/>
       <c r="B97" s="34"/>
-      <c r="C97" s="16" t="s">
-        <v>73</v>
+      <c r="C97" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="E97" s="13"/>
     </row>
     <row r="98" spans="1:5" ht="18" customHeight="1">
       <c r="A98" s="34"/>
       <c r="B98" s="34"/>
-      <c r="C98" s="16" t="s">
-        <v>73</v>
+      <c r="C98" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="E98" s="13"/>
     </row>
     <row r="99" spans="1:5" ht="18" customHeight="1">
       <c r="A99" s="34"/>
       <c r="B99" s="34"/>
-      <c r="C99" s="17" t="s">
-        <v>18</v>
+      <c r="C99" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="E99" s="13"/>
     </row>
     <row r="100" spans="1:5" ht="18" customHeight="1">
       <c r="A100" s="34"/>
       <c r="B100" s="34"/>
-      <c r="C100" s="17" t="s">
-        <v>18</v>
+      <c r="C100" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E100" s="13"/>
     </row>
     <row r="101" spans="1:5" ht="18" customHeight="1">
-      <c r="A101" s="35"/>
-      <c r="B101" s="35"/>
-      <c r="C101" s="18" t="s">
-        <v>78</v>
+      <c r="A101" s="34"/>
+      <c r="B101" s="34"/>
+      <c r="C101" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>512</v>
+        <v>147</v>
       </c>
       <c r="E101" s="13"/>
     </row>
     <row r="102" spans="1:5" ht="18" customHeight="1">
-      <c r="A102" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="B102" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>168</v>
+      <c r="A102" s="34"/>
+      <c r="B102" s="34"/>
+      <c r="C102" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="E102" s="13"/>
     </row>
     <row r="103" spans="1:5" ht="18" customHeight="1">
       <c r="A103" s="34"/>
       <c r="B103" s="34"/>
-      <c r="C103" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>169</v>
+      <c r="C103" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="E103" s="13"/>
     </row>
     <row r="104" spans="1:5" ht="18" customHeight="1">
       <c r="A104" s="34"/>
       <c r="B104" s="34"/>
-      <c r="C104" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>170</v>
+      <c r="C104" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>150</v>
       </c>
       <c r="E104" s="13"/>
     </row>
     <row r="105" spans="1:5" ht="18" customHeight="1">
-      <c r="A105" s="34"/>
-      <c r="B105" s="34"/>
-      <c r="C105" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>171</v>
+      <c r="A105" s="35"/>
+      <c r="B105" s="35"/>
+      <c r="C105" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>488</v>
       </c>
       <c r="E105" s="13"/>
     </row>
     <row r="106" spans="1:5" ht="18" customHeight="1">
-      <c r="A106" s="34"/>
-      <c r="B106" s="34"/>
+      <c r="A106" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B106" s="33" t="s">
+        <v>152</v>
+      </c>
       <c r="C106" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E106" s="13"/>
     </row>
@@ -4262,371 +4686,371 @@
         <v>65</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="E107" s="13"/>
     </row>
     <row r="108" spans="1:5" ht="18" customHeight="1">
       <c r="A108" s="34"/>
       <c r="B108" s="34"/>
-      <c r="C108" s="16" t="s">
-        <v>73</v>
+      <c r="C108" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E108" s="13"/>
     </row>
     <row r="109" spans="1:5" ht="18" customHeight="1">
       <c r="A109" s="34"/>
       <c r="B109" s="34"/>
-      <c r="C109" s="16" t="s">
-        <v>73</v>
+      <c r="C109" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="E109" s="13"/>
     </row>
     <row r="110" spans="1:5" ht="18" customHeight="1">
       <c r="A110" s="34"/>
       <c r="B110" s="34"/>
-      <c r="C110" s="16" t="s">
-        <v>73</v>
+      <c r="C110" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E110" s="13"/>
     </row>
     <row r="111" spans="1:5" ht="18" customHeight="1">
       <c r="A111" s="34"/>
       <c r="B111" s="34"/>
-      <c r="C111" s="16" t="s">
-        <v>73</v>
+      <c r="C111" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>176</v>
+        <v>534</v>
       </c>
       <c r="E111" s="13"/>
     </row>
     <row r="112" spans="1:5" ht="18" customHeight="1">
       <c r="A112" s="34"/>
       <c r="B112" s="34"/>
-      <c r="C112" s="17" t="s">
-        <v>18</v>
+      <c r="C112" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="E112" s="13"/>
     </row>
     <row r="113" spans="1:5" ht="18" customHeight="1">
       <c r="A113" s="34"/>
       <c r="B113" s="34"/>
-      <c r="C113" s="17" t="s">
-        <v>18</v>
+      <c r="C113" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="E113" s="13"/>
     </row>
     <row r="114" spans="1:5" ht="18" customHeight="1">
-      <c r="A114" s="35"/>
-      <c r="B114" s="35"/>
-      <c r="C114" s="18" t="s">
-        <v>78</v>
+      <c r="A114" s="34"/>
+      <c r="B114" s="34"/>
+      <c r="C114" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>509</v>
+        <v>159</v>
       </c>
       <c r="E114" s="13"/>
     </row>
     <row r="115" spans="1:5" ht="18" customHeight="1">
-      <c r="A115" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="B115" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>181</v>
+      <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D115" s="14" t="s">
+        <v>160</v>
       </c>
       <c r="E115" s="13"/>
     </row>
     <row r="116" spans="1:5" ht="18" customHeight="1">
       <c r="A116" s="34"/>
       <c r="B116" s="34"/>
-      <c r="C116" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D116" s="14" t="s">
-        <v>182</v>
+      <c r="C116" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>535</v>
       </c>
       <c r="E116" s="13"/>
     </row>
     <row r="117" spans="1:5" ht="18" customHeight="1">
       <c r="A117" s="34"/>
       <c r="B117" s="34"/>
-      <c r="C117" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>183</v>
+      <c r="C117" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D117" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="E117" s="13"/>
     </row>
     <row r="118" spans="1:5" ht="18" customHeight="1">
-      <c r="A118" s="34"/>
-      <c r="B118" s="34"/>
-      <c r="C118" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D118" s="14" t="s">
-        <v>184</v>
+      <c r="A118" s="35"/>
+      <c r="B118" s="35"/>
+      <c r="C118" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>485</v>
       </c>
       <c r="E118" s="13"/>
     </row>
     <row r="119" spans="1:5" ht="18" customHeight="1">
-      <c r="A119" s="34"/>
-      <c r="B119" s="34"/>
+      <c r="A119" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="B119" s="33" t="s">
+        <v>163</v>
+      </c>
       <c r="C119" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E119" s="13"/>
     </row>
     <row r="120" spans="1:5" ht="18" customHeight="1">
       <c r="A120" s="34"/>
       <c r="B120" s="34"/>
-      <c r="C120" s="15" t="s">
-        <v>70</v>
+      <c r="C120" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="E120" s="13"/>
     </row>
     <row r="121" spans="1:5" ht="18" customHeight="1">
       <c r="A121" s="34"/>
       <c r="B121" s="34"/>
-      <c r="C121" s="15" t="s">
-        <v>70</v>
+      <c r="C121" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="E121" s="13"/>
     </row>
     <row r="122" spans="1:5" ht="18" customHeight="1">
       <c r="A122" s="34"/>
       <c r="B122" s="34"/>
-      <c r="C122" s="16" t="s">
-        <v>73</v>
+      <c r="C122" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E122" s="13"/>
     </row>
     <row r="123" spans="1:5" ht="18" customHeight="1">
       <c r="A123" s="34"/>
       <c r="B123" s="34"/>
-      <c r="C123" s="16" t="s">
-        <v>73</v>
+      <c r="C123" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E123" s="13"/>
     </row>
     <row r="124" spans="1:5" ht="18" customHeight="1">
       <c r="A124" s="34"/>
       <c r="B124" s="34"/>
-      <c r="C124" s="16" t="s">
-        <v>73</v>
+      <c r="C124" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="E124" s="13"/>
     </row>
     <row r="125" spans="1:5" ht="18" customHeight="1">
       <c r="A125" s="34"/>
       <c r="B125" s="34"/>
-      <c r="C125" s="16" t="s">
+      <c r="C125" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E125" s="13"/>
+    </row>
+    <row r="126" spans="1:5" ht="18" customHeight="1">
+      <c r="A126" s="34"/>
+      <c r="B126" s="34"/>
+      <c r="C126" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D125" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E125" s="13"/>
-    </row>
-    <row r="126" spans="1:5" ht="18" customHeight="1">
-      <c r="A126" s="35"/>
-      <c r="B126" s="35"/>
-      <c r="C126" s="18" t="s">
-        <v>78</v>
-      </c>
       <c r="D126" s="14" t="s">
-        <v>513</v>
+        <v>146</v>
       </c>
       <c r="E126" s="13"/>
     </row>
     <row r="127" spans="1:5" ht="18" customHeight="1">
-      <c r="A127" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="B127" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="C127" s="11" t="s">
-        <v>65</v>
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E127" s="13"/>
     </row>
     <row r="128" spans="1:5" ht="18" customHeight="1">
       <c r="A128" s="34"/>
       <c r="B128" s="34"/>
-      <c r="C128" s="11" t="s">
-        <v>65</v>
+      <c r="C128" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="E128" s="13"/>
     </row>
     <row r="129" spans="1:5" ht="18" customHeight="1">
       <c r="A129" s="34"/>
       <c r="B129" s="34"/>
-      <c r="C129" s="11" t="s">
-        <v>65</v>
+      <c r="C129" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="E129" s="13"/>
     </row>
     <row r="130" spans="1:5" ht="18" customHeight="1">
-      <c r="A130" s="34"/>
-      <c r="B130" s="34"/>
-      <c r="C130" s="11" t="s">
-        <v>65</v>
+      <c r="A130" s="35"/>
+      <c r="B130" s="35"/>
+      <c r="C130" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>196</v>
+        <v>489</v>
       </c>
       <c r="E130" s="13"/>
     </row>
     <row r="131" spans="1:5" ht="18" customHeight="1">
-      <c r="A131" s="34"/>
-      <c r="B131" s="34"/>
-      <c r="C131" s="16" t="s">
-        <v>73</v>
+      <c r="A131" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B131" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E131" s="13"/>
     </row>
     <row r="132" spans="1:5" ht="18" customHeight="1">
       <c r="A132" s="34"/>
       <c r="B132" s="34"/>
-      <c r="C132" s="16" t="s">
-        <v>73</v>
+      <c r="C132" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="E132" s="13"/>
     </row>
     <row r="133" spans="1:5" ht="18" customHeight="1">
       <c r="A133" s="34"/>
       <c r="B133" s="34"/>
-      <c r="C133" s="16" t="s">
+      <c r="C133" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="E133" s="13"/>
+    </row>
+    <row r="134" spans="1:5" ht="18" customHeight="1">
+      <c r="A134" s="34"/>
+      <c r="B134" s="34"/>
+      <c r="C134" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D134" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="E134" s="13"/>
+    </row>
+    <row r="135" spans="1:5" ht="18" customHeight="1">
+      <c r="A135" s="34"/>
+      <c r="B135" s="34"/>
+      <c r="C135" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D133" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E133" s="13"/>
-    </row>
-    <row r="134" spans="1:5" ht="18" customHeight="1">
-      <c r="A134" s="35"/>
-      <c r="B134" s="35"/>
-      <c r="C134" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D134" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E134" s="13"/>
-    </row>
-    <row r="135" spans="1:5" ht="18" customHeight="1">
-      <c r="A135" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="B135" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="D135" s="12" t="s">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="E135" s="13"/>
     </row>
     <row r="136" spans="1:5" ht="18" customHeight="1">
       <c r="A136" s="34"/>
       <c r="B136" s="34"/>
-      <c r="C136" s="11" t="s">
-        <v>65</v>
+      <c r="C136" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="E136" s="13"/>
     </row>
     <row r="137" spans="1:5" ht="18" customHeight="1">
       <c r="A137" s="34"/>
       <c r="B137" s="34"/>
-      <c r="C137" s="11" t="s">
-        <v>65</v>
+      <c r="C137" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="E137" s="13"/>
     </row>
     <row r="138" spans="1:5" ht="18" customHeight="1">
-      <c r="A138" s="34"/>
-      <c r="B138" s="34"/>
-      <c r="C138" s="11" t="s">
-        <v>65</v>
+      <c r="A138" s="35"/>
+      <c r="B138" s="35"/>
+      <c r="C138" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="E138" s="13"/>
     </row>
     <row r="139" spans="1:5" ht="18" customHeight="1">
-      <c r="A139" s="34"/>
-      <c r="B139" s="34"/>
+      <c r="A139" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B139" s="33" t="s">
+        <v>182</v>
+      </c>
       <c r="C139" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E139" s="13"/>
     </row>
@@ -4637,7 +5061,7 @@
         <v>65</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="E140" s="13"/>
     </row>
@@ -4648,235 +5072,235 @@
         <v>65</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="E141" s="13"/>
     </row>
     <row r="142" spans="1:5" ht="18" customHeight="1">
       <c r="A142" s="34"/>
       <c r="B142" s="34"/>
-      <c r="C142" s="15" t="s">
-        <v>70</v>
+      <c r="C142" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D142" s="14" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="E142" s="13"/>
     </row>
     <row r="143" spans="1:5" ht="18" customHeight="1">
       <c r="A143" s="34"/>
       <c r="B143" s="34"/>
-      <c r="C143" s="16" t="s">
-        <v>73</v>
+      <c r="C143" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="E143" s="13"/>
     </row>
     <row r="144" spans="1:5" ht="18" customHeight="1">
       <c r="A144" s="34"/>
       <c r="B144" s="34"/>
-      <c r="C144" s="16" t="s">
-        <v>73</v>
+      <c r="C144" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="E144" s="13"/>
     </row>
     <row r="145" spans="1:5" ht="18" customHeight="1">
       <c r="A145" s="34"/>
       <c r="B145" s="34"/>
-      <c r="C145" s="16" t="s">
-        <v>73</v>
+      <c r="C145" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="E145" s="13"/>
     </row>
     <row r="146" spans="1:5" ht="18" customHeight="1">
       <c r="A146" s="34"/>
       <c r="B146" s="34"/>
-      <c r="C146" s="16" t="s">
-        <v>73</v>
+      <c r="C146" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="D146" s="14" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E146" s="13"/>
     </row>
     <row r="147" spans="1:5" ht="18" customHeight="1">
       <c r="A147" s="34"/>
       <c r="B147" s="34"/>
-      <c r="C147" s="17" t="s">
-        <v>18</v>
+      <c r="C147" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="E147" s="13"/>
     </row>
     <row r="148" spans="1:5" ht="18" customHeight="1">
-      <c r="A148" s="35"/>
-      <c r="B148" s="35"/>
-      <c r="C148" s="18" t="s">
-        <v>78</v>
+      <c r="A148" s="34"/>
+      <c r="B148" s="34"/>
+      <c r="C148" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>509</v>
+        <v>191</v>
       </c>
       <c r="E148" s="13"/>
     </row>
     <row r="149" spans="1:5" ht="18" customHeight="1">
-      <c r="A149" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="B149" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="C149" s="11" t="s">
-        <v>65</v>
+      <c r="A149" s="34"/>
+      <c r="B149" s="34"/>
+      <c r="C149" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="E149" s="13"/>
     </row>
     <row r="150" spans="1:5" ht="18" customHeight="1">
       <c r="A150" s="34"/>
       <c r="B150" s="34"/>
-      <c r="C150" s="11" t="s">
-        <v>65</v>
+      <c r="C150" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D150" s="14" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E150" s="13"/>
     </row>
     <row r="151" spans="1:5" ht="18" customHeight="1">
       <c r="A151" s="34"/>
       <c r="B151" s="34"/>
-      <c r="C151" s="11" t="s">
-        <v>65</v>
+      <c r="C151" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E151" s="13"/>
     </row>
     <row r="152" spans="1:5" ht="18" customHeight="1">
-      <c r="A152" s="34"/>
-      <c r="B152" s="34"/>
-      <c r="C152" s="11" t="s">
-        <v>65</v>
+      <c r="A152" s="35"/>
+      <c r="B152" s="35"/>
+      <c r="C152" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>172</v>
+        <v>485</v>
       </c>
       <c r="E152" s="13"/>
     </row>
     <row r="153" spans="1:5" ht="18" customHeight="1">
-      <c r="A153" s="34"/>
-      <c r="B153" s="34"/>
-      <c r="C153" s="16" t="s">
-        <v>73</v>
+      <c r="A153" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B153" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E153" s="13"/>
     </row>
     <row r="154" spans="1:5" ht="18" customHeight="1">
       <c r="A154" s="34"/>
       <c r="B154" s="34"/>
-      <c r="C154" s="16" t="s">
-        <v>73</v>
+      <c r="C154" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D154" s="14" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="E154" s="13"/>
     </row>
     <row r="155" spans="1:5" ht="18" customHeight="1">
       <c r="A155" s="34"/>
       <c r="B155" s="34"/>
-      <c r="C155" s="16" t="s">
+      <c r="C155" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E155" s="13"/>
+    </row>
+    <row r="156" spans="1:5" ht="18" customHeight="1">
+      <c r="A156" s="34"/>
+      <c r="B156" s="34"/>
+      <c r="C156" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D156" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E156" s="13"/>
+    </row>
+    <row r="157" spans="1:5" ht="18" customHeight="1">
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D155" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E155" s="13"/>
-    </row>
-    <row r="156" spans="1:5" ht="18" customHeight="1">
-      <c r="A156" s="35"/>
-      <c r="B156" s="35"/>
-      <c r="C156" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D156" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="E156" s="13"/>
-    </row>
-    <row r="157" spans="1:5" ht="18" customHeight="1">
-      <c r="A157" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="B157" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="C157" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="D157" s="12" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="E157" s="13"/>
     </row>
     <row r="158" spans="1:5" ht="18" customHeight="1">
       <c r="A158" s="34"/>
       <c r="B158" s="34"/>
-      <c r="C158" s="11" t="s">
-        <v>65</v>
+      <c r="C158" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="E158" s="13"/>
     </row>
     <row r="159" spans="1:5" ht="18" customHeight="1">
       <c r="A159" s="34"/>
       <c r="B159" s="34"/>
-      <c r="C159" s="11" t="s">
-        <v>65</v>
+      <c r="C159" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="E159" s="13"/>
     </row>
     <row r="160" spans="1:5" ht="18" customHeight="1">
-      <c r="A160" s="34"/>
-      <c r="B160" s="34"/>
-      <c r="C160" s="11" t="s">
-        <v>65</v>
+      <c r="A160" s="35"/>
+      <c r="B160" s="35"/>
+      <c r="C160" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>226</v>
+        <v>485</v>
       </c>
       <c r="E160" s="13"/>
     </row>
     <row r="161" spans="1:5" ht="18" customHeight="1">
-      <c r="A161" s="34"/>
-      <c r="B161" s="34"/>
+      <c r="A161" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B161" s="33" t="s">
+        <v>203</v>
+      </c>
       <c r="C161" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="E161" s="13"/>
     </row>
@@ -4887,125 +5311,121 @@
         <v>65</v>
       </c>
       <c r="D162" s="14" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="E162" s="13"/>
     </row>
     <row r="163" spans="1:5" ht="18" customHeight="1">
       <c r="A163" s="34"/>
       <c r="B163" s="34"/>
-      <c r="C163" s="15" t="s">
-        <v>70</v>
+      <c r="C163" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="E163" s="13"/>
     </row>
     <row r="164" spans="1:5" ht="18" customHeight="1">
       <c r="A164" s="34"/>
       <c r="B164" s="34"/>
-      <c r="C164" s="17" t="s">
-        <v>18</v>
+      <c r="C164" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D164" s="14" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="E164" s="13"/>
     </row>
     <row r="165" spans="1:5" ht="18" customHeight="1">
-      <c r="A165" s="35"/>
-      <c r="B165" s="35"/>
-      <c r="C165" s="17" t="s">
-        <v>18</v>
+      <c r="A165" s="34"/>
+      <c r="B165" s="34"/>
+      <c r="C165" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="E165" s="13"/>
     </row>
     <row r="166" spans="1:5" ht="18" customHeight="1">
-      <c r="A166" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="B166" s="36" t="s">
-        <v>233</v>
-      </c>
+      <c r="A166" s="34"/>
+      <c r="B166" s="34"/>
       <c r="C166" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D166" s="12" t="s">
-        <v>234</v>
+      <c r="D166" s="14" t="s">
+        <v>538</v>
       </c>
       <c r="E166" s="13"/>
     </row>
     <row r="167" spans="1:5" ht="18" customHeight="1">
       <c r="A167" s="34"/>
       <c r="B167" s="34"/>
-      <c r="C167" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D167" s="14" t="s">
-        <v>235</v>
+      <c r="C167" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D167" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="E167" s="13"/>
     </row>
     <row r="168" spans="1:5" ht="18" customHeight="1">
       <c r="A168" s="34"/>
       <c r="B168" s="34"/>
-      <c r="C168" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D168" s="12" t="s">
-        <v>236</v>
+      <c r="C168" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D168" s="14" t="s">
+        <v>539</v>
       </c>
       <c r="E168" s="13"/>
     </row>
     <row r="169" spans="1:5" ht="18" customHeight="1">
-      <c r="A169" s="34"/>
-      <c r="B169" s="34"/>
-      <c r="C169" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D169" s="14" t="s">
-        <v>237</v>
+      <c r="A169" s="35"/>
+      <c r="B169" s="35"/>
+      <c r="C169" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="E169" s="13"/>
     </row>
     <row r="170" spans="1:5" ht="18" customHeight="1">
-      <c r="A170" s="34"/>
-      <c r="B170" s="34"/>
-      <c r="C170" s="16" t="s">
-        <v>73</v>
+      <c r="A170" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="B170" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="E170" s="13"/>
     </row>
     <row r="171" spans="1:5" ht="18" customHeight="1">
-      <c r="A171" s="35"/>
-      <c r="B171" s="35"/>
-      <c r="C171" s="17" t="s">
-        <v>18</v>
+      <c r="A171" s="34"/>
+      <c r="B171" s="34"/>
+      <c r="C171" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="E171" s="13"/>
     </row>
     <row r="172" spans="1:5" ht="18" customHeight="1">
-      <c r="A172" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="B172" s="36" t="s">
-        <v>241</v>
-      </c>
+      <c r="A172" s="34"/>
+      <c r="B172" s="34"/>
       <c r="C172" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="E172" s="13"/>
     </row>
@@ -5016,230 +5436,267 @@
         <v>65</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="E173" s="13"/>
     </row>
     <row r="174" spans="1:5" ht="18" customHeight="1">
       <c r="A174" s="34"/>
       <c r="B174" s="34"/>
-      <c r="C174" s="11" t="s">
-        <v>65</v>
+      <c r="C174" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="E174" s="13"/>
     </row>
     <row r="175" spans="1:5" ht="18" customHeight="1">
-      <c r="A175" s="34"/>
-      <c r="B175" s="34"/>
-      <c r="C175" s="16" t="s">
+      <c r="A175" s="35"/>
+      <c r="B175" s="35"/>
+      <c r="C175" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D175" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="E175" s="13"/>
+    </row>
+    <row r="176" spans="1:5" ht="18" customHeight="1">
+      <c r="A176" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B176" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="E176" s="13"/>
+    </row>
+    <row r="177" spans="1:5" ht="18" customHeight="1">
+      <c r="A177" s="34"/>
+      <c r="B177" s="34"/>
+      <c r="C177" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E177" s="13"/>
+    </row>
+    <row r="178" spans="1:5" ht="18" customHeight="1">
+      <c r="A178" s="34"/>
+      <c r="B178" s="34"/>
+      <c r="C178" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D175" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="E175" s="13"/>
-    </row>
-    <row r="176" spans="1:5" ht="18" customHeight="1">
-      <c r="A176" s="34"/>
-      <c r="B176" s="34"/>
-      <c r="C176" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="E176" s="13"/>
-    </row>
-    <row r="177" spans="1:5" ht="18" customHeight="1">
-      <c r="A177" s="35"/>
-      <c r="B177" s="35"/>
-      <c r="C177" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D177" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="E177" s="13"/>
-    </row>
-    <row r="178" spans="1:5" ht="18" customHeight="1">
-      <c r="A178" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="B178" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="C178" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D178" s="12" t="s">
-        <v>234</v>
+      <c r="D178" s="14" t="s">
+        <v>222</v>
       </c>
       <c r="E178" s="13"/>
     </row>
     <row r="179" spans="1:5" ht="18" customHeight="1">
       <c r="A179" s="34"/>
       <c r="B179" s="34"/>
-      <c r="C179" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>250</v>
+      <c r="C179" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="E179" s="13"/>
     </row>
     <row r="180" spans="1:5" ht="18" customHeight="1">
-      <c r="A180" s="34"/>
-      <c r="B180" s="34"/>
-      <c r="C180" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>251</v>
+      <c r="A180" s="35"/>
+      <c r="B180" s="35"/>
+      <c r="C180" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D180" s="14" t="s">
+        <v>224</v>
       </c>
       <c r="E180" s="13"/>
     </row>
     <row r="181" spans="1:5" ht="18" customHeight="1">
-      <c r="A181" s="34"/>
-      <c r="B181" s="34"/>
-      <c r="C181" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>252</v>
+      <c r="A181" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="B181" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="C181" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="E181" s="13"/>
     </row>
     <row r="182" spans="1:5" ht="18" customHeight="1">
       <c r="A182" s="34"/>
       <c r="B182" s="34"/>
-      <c r="C182" s="16" t="s">
+      <c r="C182" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D182" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="E182" s="13"/>
+    </row>
+    <row r="183" spans="1:5" ht="18" customHeight="1">
+      <c r="A183" s="34"/>
+      <c r="B183" s="34"/>
+      <c r="C183" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E183" s="13"/>
+    </row>
+    <row r="184" spans="1:5" ht="18" customHeight="1">
+      <c r="A184" s="34"/>
+      <c r="B184" s="34"/>
+      <c r="C184" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D182" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="E182" s="13"/>
-    </row>
-    <row r="183" spans="1:5" ht="18" customHeight="1">
-      <c r="A183" s="35"/>
-      <c r="B183" s="35"/>
-      <c r="C183" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D183" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E183" s="13"/>
-    </row>
-    <row r="184" spans="1:5" ht="18" customHeight="1">
-      <c r="A184" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="B184" s="36" t="s">
-        <v>254</v>
-      </c>
-      <c r="C184" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D184" s="12" t="s">
-        <v>255</v>
+      <c r="D184" s="14" t="s">
+        <v>229</v>
       </c>
       <c r="E184" s="13"/>
     </row>
     <row r="185" spans="1:5" ht="18" customHeight="1">
       <c r="A185" s="34"/>
       <c r="B185" s="34"/>
-      <c r="C185" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D185" s="14" t="s">
-        <v>256</v>
+      <c r="C185" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="E185" s="13"/>
     </row>
     <row r="186" spans="1:5" ht="18" customHeight="1">
-      <c r="A186" s="34"/>
-      <c r="B186" s="34"/>
-      <c r="C186" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D186" s="12" t="s">
-        <v>257</v>
+      <c r="A186" s="35"/>
+      <c r="B186" s="35"/>
+      <c r="C186" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D186" s="14" t="s">
+        <v>218</v>
       </c>
       <c r="E186" s="13"/>
     </row>
     <row r="187" spans="1:5" ht="18" customHeight="1">
-      <c r="A187" s="35"/>
-      <c r="B187" s="35"/>
-      <c r="C187" s="16" t="s">
+      <c r="A187" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="B187" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="C187" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E187" s="13"/>
+    </row>
+    <row r="188" spans="1:5" ht="18" customHeight="1">
+      <c r="A188" s="34"/>
+      <c r="B188" s="34"/>
+      <c r="C188" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D188" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E188" s="13"/>
+    </row>
+    <row r="189" spans="1:5" ht="18" customHeight="1">
+      <c r="A189" s="34"/>
+      <c r="B189" s="34"/>
+      <c r="C189" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E189" s="13"/>
+    </row>
+    <row r="190" spans="1:5" ht="18" customHeight="1">
+      <c r="A190" s="35"/>
+      <c r="B190" s="35"/>
+      <c r="C190" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D187" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="E187" s="13"/>
+      <c r="D190" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="E190" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E187" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A2:E190" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="55">
-    <mergeCell ref="B178:B183"/>
-    <mergeCell ref="B184:B187"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="A172:A177"/>
-    <mergeCell ref="B115:B126"/>
-    <mergeCell ref="B63:B68"/>
-    <mergeCell ref="B57:B62"/>
-    <mergeCell ref="A149:A156"/>
-    <mergeCell ref="B172:B177"/>
-    <mergeCell ref="A157:A165"/>
-    <mergeCell ref="B166:B171"/>
-    <mergeCell ref="A184:A187"/>
-    <mergeCell ref="B51:B56"/>
-    <mergeCell ref="B102:B114"/>
-    <mergeCell ref="B157:B165"/>
-    <mergeCell ref="A166:A171"/>
-    <mergeCell ref="A3:A13"/>
-    <mergeCell ref="B149:B156"/>
-    <mergeCell ref="B21:B26"/>
-    <mergeCell ref="B135:B148"/>
-    <mergeCell ref="B73:B76"/>
-    <mergeCell ref="A91:A101"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B38:B43"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="A135:A148"/>
-    <mergeCell ref="B44:B50"/>
-    <mergeCell ref="A102:A114"/>
-    <mergeCell ref="B127:B134"/>
+    <mergeCell ref="A181:A186"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B95:B105"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="A41:A48"/>
+    <mergeCell ref="A68:A73"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="A32:A40"/>
+    <mergeCell ref="A119:A130"/>
+    <mergeCell ref="A131:A138"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A69:A72"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="A44:A50"/>
-    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="B32:B40"/>
     <mergeCell ref="B3:B13"/>
-    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="A78:A80"/>
     <mergeCell ref="B14:B20"/>
     <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A178:A183"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B91:B101"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="A38:A43"/>
-    <mergeCell ref="A63:A68"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="B69:B72"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="A57:A62"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="A115:A126"/>
-    <mergeCell ref="A127:A134"/>
+    <mergeCell ref="A3:A13"/>
+    <mergeCell ref="B153:B160"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="B139:B152"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="A95:A105"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="A139:A152"/>
+    <mergeCell ref="B49:B55"/>
+    <mergeCell ref="A106:A118"/>
+    <mergeCell ref="B131:B138"/>
+    <mergeCell ref="B181:B186"/>
+    <mergeCell ref="B187:B190"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A176:A180"/>
+    <mergeCell ref="B119:B130"/>
+    <mergeCell ref="B68:B73"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="A153:A160"/>
+    <mergeCell ref="B176:B180"/>
+    <mergeCell ref="A161:A169"/>
+    <mergeCell ref="B170:B175"/>
+    <mergeCell ref="A187:A190"/>
+    <mergeCell ref="B56:B61"/>
+    <mergeCell ref="B106:B118"/>
+    <mergeCell ref="B161:B169"/>
+    <mergeCell ref="A170:A175"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5260,22 +5717,22 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+        <v>236</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="22" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>63</v>
@@ -5286,31 +5743,31 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="E3" s="13"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>268</v>
+      <c r="A4" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>245</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="E4" s="13"/>
     </row>
@@ -5318,10 +5775,10 @@
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="E5" s="13"/>
     </row>
@@ -5329,10 +5786,10 @@
       <c r="A6" s="34"/>
       <c r="B6" s="34"/>
       <c r="C6" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="E6" s="13"/>
     </row>
@@ -5340,10 +5797,10 @@
       <c r="A7" s="34"/>
       <c r="B7" s="34"/>
       <c r="C7" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="E7" s="13"/>
     </row>
@@ -5351,10 +5808,10 @@
       <c r="A8" s="34"/>
       <c r="B8" s="34"/>
       <c r="C8" s="11" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="E8" s="13"/>
     </row>
@@ -5362,10 +5819,10 @@
       <c r="A9" s="34"/>
       <c r="B9" s="34"/>
       <c r="C9" s="20" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="E9" s="13"/>
     </row>
@@ -5373,10 +5830,10 @@
       <c r="A10" s="34"/>
       <c r="B10" s="34"/>
       <c r="C10" s="20" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="E10" s="13"/>
     </row>
@@ -5384,10 +5841,10 @@
       <c r="A11" s="34"/>
       <c r="B11" s="34"/>
       <c r="C11" s="20" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="E11" s="13"/>
     </row>
@@ -5395,10 +5852,10 @@
       <c r="A12" s="34"/>
       <c r="B12" s="34"/>
       <c r="C12" s="20" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="E12" s="13"/>
     </row>
@@ -5406,10 +5863,10 @@
       <c r="A13" s="34"/>
       <c r="B13" s="34"/>
       <c r="C13" s="20" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="E13" s="13"/>
     </row>
@@ -5417,10 +5874,10 @@
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="20" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E14" s="13"/>
     </row>
@@ -5428,10 +5885,10 @@
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
       <c r="C15" s="20" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="E15" s="13"/>
     </row>
@@ -5439,10 +5896,10 @@
       <c r="A16" s="34"/>
       <c r="B16" s="34"/>
       <c r="C16" s="20" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="E16" s="13"/>
     </row>
@@ -5450,10 +5907,10 @@
       <c r="A17" s="34"/>
       <c r="B17" s="34"/>
       <c r="C17" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="E17" s="13"/>
     </row>
@@ -5461,25 +5918,25 @@
       <c r="A18" s="35"/>
       <c r="B18" s="35"/>
       <c r="C18" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
-      <c r="A19" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>284</v>
+      <c r="A19" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>261</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="E19" s="13"/>
     </row>
@@ -5487,10 +5944,10 @@
       <c r="A20" s="34"/>
       <c r="B20" s="34"/>
       <c r="C20" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="E20" s="13"/>
     </row>
@@ -5498,10 +5955,10 @@
       <c r="A21" s="34"/>
       <c r="B21" s="34"/>
       <c r="C21" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="E21" s="13"/>
     </row>
@@ -5509,10 +5966,10 @@
       <c r="A22" s="34"/>
       <c r="B22" s="34"/>
       <c r="C22" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="E22" s="13"/>
     </row>
@@ -5520,25 +5977,25 @@
       <c r="A23" s="35"/>
       <c r="B23" s="35"/>
       <c r="C23" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="E23" s="13"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1">
-      <c r="A24" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>289</v>
+      <c r="A24" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>266</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="E24" s="13"/>
     </row>
@@ -5546,10 +6003,10 @@
       <c r="A25" s="34"/>
       <c r="B25" s="34"/>
       <c r="C25" s="20" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="E25" s="13"/>
     </row>
@@ -5557,10 +6014,10 @@
       <c r="A26" s="34"/>
       <c r="B26" s="34"/>
       <c r="C26" s="20" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="E26" s="13"/>
     </row>
@@ -5568,10 +6025,10 @@
       <c r="A27" s="34"/>
       <c r="B27" s="34"/>
       <c r="C27" s="20" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="E27" s="13"/>
     </row>
@@ -5579,25 +6036,25 @@
       <c r="A28" s="35"/>
       <c r="B28" s="35"/>
       <c r="C28" s="20" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="E28" s="13"/>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1">
-      <c r="A29" s="33" t="s">
-        <v>514</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>294</v>
+      <c r="A29" s="36" t="s">
+        <v>490</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>271</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="E29" s="13"/>
     </row>
@@ -5605,10 +6062,10 @@
       <c r="A30" s="34"/>
       <c r="B30" s="34"/>
       <c r="C30" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
       <c r="E30" s="13"/>
     </row>
@@ -5616,10 +6073,10 @@
       <c r="A31" s="34"/>
       <c r="B31" s="34"/>
       <c r="C31" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="E31" s="13"/>
     </row>
@@ -5627,25 +6084,25 @@
       <c r="A32" s="35"/>
       <c r="B32" s="35"/>
       <c r="C32" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="E32" s="13"/>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1">
-      <c r="A33" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>299</v>
+      <c r="A33" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>276</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="E33" s="13"/>
     </row>
@@ -5653,10 +6110,10 @@
       <c r="A34" s="34"/>
       <c r="B34" s="34"/>
       <c r="C34" s="20" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="E34" s="13"/>
     </row>
@@ -5664,10 +6121,10 @@
       <c r="A35" s="34"/>
       <c r="B35" s="34"/>
       <c r="C35" s="20" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="E35" s="13"/>
     </row>
@@ -5675,25 +6132,25 @@
       <c r="A36" s="35"/>
       <c r="B36" s="35"/>
       <c r="C36" s="20" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="E36" s="13"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1">
-      <c r="A37" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>306</v>
+      <c r="A37" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>283</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="E37" s="13"/>
     </row>
@@ -5704,7 +6161,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="E38" s="13"/>
     </row>
@@ -5715,7 +6172,7 @@
         <v>17</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="E39" s="13"/>
     </row>
@@ -5723,25 +6180,25 @@
       <c r="A40" s="35"/>
       <c r="B40" s="35"/>
       <c r="C40" s="20" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="E40" s="13"/>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1">
-      <c r="A41" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>312</v>
+      <c r="A41" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>289</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="E41" s="13"/>
     </row>
@@ -5749,25 +6206,25 @@
       <c r="A42" s="35"/>
       <c r="B42" s="35"/>
       <c r="C42" s="20" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="E42" s="13"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1">
-      <c r="A43" s="33" t="s">
-        <v>317</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>318</v>
+      <c r="A43" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="E43" s="13"/>
     </row>
@@ -5775,10 +6232,10 @@
       <c r="A44" s="34"/>
       <c r="B44" s="34"/>
       <c r="C44" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
       <c r="E44" s="13"/>
     </row>
@@ -5786,10 +6243,10 @@
       <c r="A45" s="34"/>
       <c r="B45" s="34"/>
       <c r="C45" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="E45" s="13"/>
     </row>
@@ -5797,10 +6254,10 @@
       <c r="A46" s="34"/>
       <c r="B46" s="34"/>
       <c r="C46" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="E46" s="13"/>
     </row>
@@ -5808,25 +6265,25 @@
       <c r="A47" s="35"/>
       <c r="B47" s="35"/>
       <c r="C47" s="20" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="E47" s="13"/>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1">
-      <c r="A48" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="B48" s="36" t="s">
-        <v>322</v>
+      <c r="A48" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" s="33" t="s">
+        <v>299</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="E48" s="13"/>
     </row>
@@ -5834,10 +6291,10 @@
       <c r="A49" s="34"/>
       <c r="B49" s="34"/>
       <c r="C49" s="20" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="E49" s="13"/>
     </row>
@@ -5845,10 +6302,10 @@
       <c r="A50" s="34"/>
       <c r="B50" s="34"/>
       <c r="C50" s="18" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="E50" s="13"/>
     </row>
@@ -5856,10 +6313,10 @@
       <c r="A51" s="34"/>
       <c r="B51" s="34"/>
       <c r="C51" s="20" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="E51" s="13"/>
     </row>
@@ -5867,10 +6324,10 @@
       <c r="A52" s="34"/>
       <c r="B52" s="34"/>
       <c r="C52" s="20" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="E52" s="13"/>
     </row>
@@ -5878,25 +6335,25 @@
       <c r="A53" s="35"/>
       <c r="B53" s="35"/>
       <c r="C53" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
       <c r="E53" s="13"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1">
-      <c r="A54" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="B54" s="36" t="s">
-        <v>328</v>
+      <c r="A54" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>305</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="E54" s="13"/>
     </row>
@@ -5904,10 +6361,10 @@
       <c r="A55" s="34"/>
       <c r="B55" s="34"/>
       <c r="C55" s="20" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="E55" s="13"/>
     </row>
@@ -5915,10 +6372,10 @@
       <c r="A56" s="34"/>
       <c r="B56" s="34"/>
       <c r="C56" s="20" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>470</v>
+        <v>447</v>
       </c>
       <c r="E56" s="13"/>
     </row>
@@ -5926,25 +6383,25 @@
       <c r="A57" s="35"/>
       <c r="B57" s="35"/>
       <c r="C57" s="20" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="E57" s="13"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1">
-      <c r="A58" s="33" t="s">
-        <v>516</v>
-      </c>
-      <c r="B58" s="36" t="s">
-        <v>330</v>
+      <c r="A58" s="36" t="s">
+        <v>492</v>
+      </c>
+      <c r="B58" s="33" t="s">
+        <v>307</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="E58" s="13"/>
     </row>
@@ -5952,10 +6409,10 @@
       <c r="A59" s="34"/>
       <c r="B59" s="34"/>
       <c r="C59" s="20" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="E59" s="13"/>
     </row>
@@ -5963,10 +6420,10 @@
       <c r="A60" s="34"/>
       <c r="B60" s="34"/>
       <c r="C60" s="20" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="E60" s="13"/>
     </row>
@@ -5974,10 +6431,10 @@
       <c r="A61" s="34"/>
       <c r="B61" s="34"/>
       <c r="C61" s="20" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="E61" s="13"/>
     </row>
@@ -5985,10 +6442,10 @@
       <c r="A62" s="34"/>
       <c r="B62" s="34"/>
       <c r="C62" s="20" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="E62" s="13"/>
     </row>
@@ -5996,10 +6453,10 @@
       <c r="A63" s="34"/>
       <c r="B63" s="34"/>
       <c r="C63" s="20" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="E63" s="13"/>
     </row>
@@ -6007,10 +6464,10 @@
       <c r="A64" s="34"/>
       <c r="B64" s="34"/>
       <c r="C64" s="20" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="E64" s="13"/>
     </row>
@@ -6018,10 +6475,10 @@
       <c r="A65" s="34"/>
       <c r="B65" s="34"/>
       <c r="C65" s="20" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="E65" s="13"/>
     </row>
@@ -6029,10 +6486,10 @@
       <c r="A66" s="34"/>
       <c r="B66" s="34"/>
       <c r="C66" s="20" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="E66" s="13"/>
     </row>
@@ -6040,25 +6497,25 @@
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="20" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
       <c r="E67" s="13"/>
     </row>
     <row r="68" spans="1:5" ht="18" customHeight="1">
-      <c r="A68" s="33" t="s">
+      <c r="A68" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B68" s="36" t="s">
-        <v>341</v>
+      <c r="B68" s="33" t="s">
+        <v>318</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="E68" s="13"/>
     </row>
@@ -6066,10 +6523,10 @@
       <c r="A69" s="34"/>
       <c r="B69" s="34"/>
       <c r="C69" s="20" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
       <c r="E69" s="13"/>
     </row>
@@ -6077,10 +6534,10 @@
       <c r="A70" s="34"/>
       <c r="B70" s="34"/>
       <c r="C70" s="20" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="E70" s="13"/>
     </row>
@@ -6088,10 +6545,10 @@
       <c r="A71" s="34"/>
       <c r="B71" s="34"/>
       <c r="C71" s="20" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="E71" s="13"/>
     </row>
@@ -6099,10 +6556,10 @@
       <c r="A72" s="34"/>
       <c r="B72" s="34"/>
       <c r="C72" s="20" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="E72" s="13"/>
     </row>
@@ -6110,25 +6567,25 @@
       <c r="A73" s="35"/>
       <c r="B73" s="35"/>
       <c r="C73" s="20" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="E73" s="13"/>
     </row>
     <row r="74" spans="1:5" ht="18" customHeight="1">
-      <c r="A74" s="33" t="s">
-        <v>351</v>
-      </c>
-      <c r="B74" s="36" t="s">
-        <v>352</v>
+      <c r="A74" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="B74" s="33" t="s">
+        <v>329</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="E74" s="13"/>
     </row>
@@ -6136,10 +6593,10 @@
       <c r="A75" s="34"/>
       <c r="B75" s="34"/>
       <c r="C75" s="20" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="E75" s="13"/>
     </row>
@@ -6147,10 +6604,10 @@
       <c r="A76" s="34"/>
       <c r="B76" s="34"/>
       <c r="C76" s="20" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="E76" s="13"/>
     </row>
@@ -6158,10 +6615,10 @@
       <c r="A77" s="34"/>
       <c r="B77" s="34"/>
       <c r="C77" s="20" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="E77" s="13"/>
     </row>
@@ -6169,10 +6626,10 @@
       <c r="A78" s="34"/>
       <c r="B78" s="34"/>
       <c r="C78" s="20" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="E78" s="13"/>
     </row>
@@ -6180,10 +6637,10 @@
       <c r="A79" s="34"/>
       <c r="B79" s="34"/>
       <c r="C79" s="20" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="E79" s="13"/>
     </row>
@@ -6191,25 +6648,25 @@
       <c r="A80" s="35"/>
       <c r="B80" s="35"/>
       <c r="C80" s="20" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="E80" s="13"/>
     </row>
     <row r="81" spans="1:5" ht="18" customHeight="1">
-      <c r="A81" s="33" t="s">
-        <v>361</v>
-      </c>
-      <c r="B81" s="36" t="s">
-        <v>362</v>
+      <c r="A81" s="36" t="s">
+        <v>338</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>339</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="E81" s="13"/>
     </row>
@@ -6217,10 +6674,10 @@
       <c r="A82" s="34"/>
       <c r="B82" s="34"/>
       <c r="C82" s="20" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="E82" s="13"/>
     </row>
@@ -6228,10 +6685,10 @@
       <c r="A83" s="34"/>
       <c r="B83" s="34"/>
       <c r="C83" s="20" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="E83" s="13"/>
     </row>
@@ -6239,10 +6696,10 @@
       <c r="A84" s="34"/>
       <c r="B84" s="34"/>
       <c r="C84" s="20" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="E84" s="13"/>
     </row>
@@ -6250,25 +6707,25 @@
       <c r="A85" s="35"/>
       <c r="B85" s="35"/>
       <c r="C85" s="20" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="E85" s="13"/>
     </row>
     <row r="86" spans="1:5" ht="18" customHeight="1">
-      <c r="A86" s="33" t="s">
-        <v>368</v>
-      </c>
-      <c r="B86" s="36" t="s">
-        <v>369</v>
+      <c r="A86" s="36" t="s">
+        <v>345</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>346</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="E86" s="13"/>
     </row>
@@ -6276,10 +6733,10 @@
       <c r="A87" s="34"/>
       <c r="B87" s="34"/>
       <c r="C87" s="20" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="E87" s="13"/>
     </row>
@@ -6287,10 +6744,10 @@
       <c r="A88" s="34"/>
       <c r="B88" s="34"/>
       <c r="C88" s="20" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="E88" s="13"/>
     </row>
@@ -6298,10 +6755,10 @@
       <c r="A89" s="34"/>
       <c r="B89" s="34"/>
       <c r="C89" s="20" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="E89" s="13"/>
     </row>
@@ -6309,10 +6766,10 @@
       <c r="A90" s="34"/>
       <c r="B90" s="34"/>
       <c r="C90" s="20" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="E90" s="13"/>
     </row>
@@ -6320,10 +6777,10 @@
       <c r="A91" s="34"/>
       <c r="B91" s="34"/>
       <c r="C91" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="E91" s="13"/>
     </row>
@@ -6331,25 +6788,25 @@
       <c r="A92" s="35"/>
       <c r="B92" s="35"/>
       <c r="C92" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="E92" s="13"/>
     </row>
     <row r="93" spans="1:5" ht="18" customHeight="1">
-      <c r="A93" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="B93" s="36" t="s">
-        <v>379</v>
+      <c r="A93" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>356</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="E93" s="13"/>
     </row>
@@ -6357,10 +6814,10 @@
       <c r="A94" s="34"/>
       <c r="B94" s="34"/>
       <c r="C94" s="20" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="E94" s="13"/>
     </row>
@@ -6368,10 +6825,10 @@
       <c r="A95" s="34"/>
       <c r="B95" s="34"/>
       <c r="C95" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="E95" s="13"/>
     </row>
@@ -6379,25 +6836,25 @@
       <c r="A96" s="35"/>
       <c r="B96" s="35"/>
       <c r="C96" s="20" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="E96" s="13"/>
     </row>
     <row r="97" spans="1:5" ht="18" customHeight="1">
-      <c r="A97" s="33" t="s">
-        <v>384</v>
-      </c>
-      <c r="B97" s="36" t="s">
-        <v>385</v>
+      <c r="A97" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="B97" s="33" t="s">
+        <v>362</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="E97" s="13"/>
     </row>
@@ -6405,10 +6862,10 @@
       <c r="A98" s="34"/>
       <c r="B98" s="34"/>
       <c r="C98" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E98" s="13"/>
     </row>
@@ -6416,25 +6873,25 @@
       <c r="A99" s="35"/>
       <c r="B99" s="35"/>
       <c r="C99" s="20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="E99" s="13"/>
     </row>
     <row r="100" spans="1:5" ht="18" customHeight="1">
-      <c r="A100" s="33" t="s">
-        <v>389</v>
-      </c>
-      <c r="B100" s="36" t="s">
-        <v>390</v>
+      <c r="A100" s="36" t="s">
+        <v>366</v>
+      </c>
+      <c r="B100" s="33" t="s">
+        <v>367</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="E100" s="13"/>
     </row>
@@ -6442,10 +6899,10 @@
       <c r="A101" s="34"/>
       <c r="B101" s="34"/>
       <c r="C101" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="E101" s="13"/>
     </row>
@@ -6453,10 +6910,10 @@
       <c r="A102" s="34"/>
       <c r="B102" s="34"/>
       <c r="C102" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="E102" s="13"/>
     </row>
@@ -6464,25 +6921,25 @@
       <c r="A103" s="35"/>
       <c r="B103" s="35"/>
       <c r="C103" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="E103" s="13"/>
     </row>
     <row r="104" spans="1:5" ht="18" customHeight="1">
-      <c r="A104" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="B104" s="36" t="s">
-        <v>396</v>
+      <c r="A104" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="B104" s="33" t="s">
+        <v>373</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="E104" s="13"/>
     </row>
@@ -6490,10 +6947,10 @@
       <c r="A105" s="34"/>
       <c r="B105" s="34"/>
       <c r="C105" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="E105" s="13"/>
     </row>
@@ -6501,10 +6958,10 @@
       <c r="A106" s="34"/>
       <c r="B106" s="34"/>
       <c r="C106" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="E106" s="13"/>
     </row>
@@ -6512,10 +6969,10 @@
       <c r="A107" s="34"/>
       <c r="B107" s="34"/>
       <c r="C107" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="E107" s="13"/>
     </row>
@@ -6523,25 +6980,25 @@
       <c r="A108" s="35"/>
       <c r="B108" s="35"/>
       <c r="C108" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="E108" s="13"/>
     </row>
     <row r="109" spans="1:5" ht="18" customHeight="1">
-      <c r="A109" s="33" t="s">
-        <v>402</v>
-      </c>
-      <c r="B109" s="36" t="s">
-        <v>403</v>
+      <c r="A109" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="B109" s="33" t="s">
+        <v>380</v>
       </c>
       <c r="C109" s="20" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="E109" s="13"/>
     </row>
@@ -6549,10 +7006,10 @@
       <c r="A110" s="34"/>
       <c r="B110" s="34"/>
       <c r="C110" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="E110" s="13"/>
     </row>
@@ -6560,10 +7017,10 @@
       <c r="A111" s="34"/>
       <c r="B111" s="34"/>
       <c r="C111" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="E111" s="13"/>
     </row>
@@ -6571,25 +7028,25 @@
       <c r="A112" s="35"/>
       <c r="B112" s="35"/>
       <c r="C112" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="E112" s="13"/>
     </row>
     <row r="113" spans="1:5" ht="18" customHeight="1">
-      <c r="A113" s="33" t="s">
-        <v>404</v>
-      </c>
-      <c r="B113" s="36" t="s">
-        <v>405</v>
+      <c r="A113" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="B113" s="33" t="s">
+        <v>382</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="E113" s="13"/>
     </row>
@@ -6597,10 +7054,10 @@
       <c r="A114" s="34"/>
       <c r="B114" s="34"/>
       <c r="C114" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
       <c r="E114" s="13"/>
     </row>
@@ -6608,183 +7065,218 @@
       <c r="A115" s="35"/>
       <c r="B115" s="35"/>
       <c r="C115" s="20" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="E115" s="13"/>
     </row>
     <row r="116" spans="1:5" ht="18" customHeight="1">
-      <c r="A116" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="B116" s="36" t="s">
-        <v>410</v>
+      <c r="A116" s="36" t="s">
+        <v>386</v>
+      </c>
+      <c r="B116" s="33" t="s">
+        <v>387</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="E116" s="13"/>
     </row>
     <row r="117" spans="1:5" ht="18" customHeight="1">
       <c r="A117" s="34"/>
-      <c r="B117" s="38"/>
+      <c r="B117" s="37"/>
       <c r="C117" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="E117" s="13"/>
     </row>
     <row r="118" spans="1:5" ht="18" customHeight="1">
       <c r="A118" s="35"/>
-      <c r="B118" s="37"/>
+      <c r="B118" s="38"/>
       <c r="C118" s="20" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="E118" s="13"/>
     </row>
     <row r="119" spans="1:5" ht="18" customHeight="1">
-      <c r="A119" s="33" t="s">
-        <v>414</v>
-      </c>
-      <c r="B119" s="36" t="s">
-        <v>415</v>
+      <c r="A119" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="B119" s="33" t="s">
+        <v>392</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="E119" s="13"/>
     </row>
     <row r="120" spans="1:5" ht="18" customHeight="1">
       <c r="A120" s="34"/>
-      <c r="B120" s="38"/>
+      <c r="B120" s="37"/>
       <c r="C120" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="E120" s="13"/>
     </row>
     <row r="121" spans="1:5" ht="18" customHeight="1">
       <c r="A121" s="35"/>
-      <c r="B121" s="37"/>
+      <c r="B121" s="38"/>
       <c r="C121" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="E121" s="13"/>
     </row>
     <row r="122" spans="1:5" ht="18" customHeight="1">
       <c r="A122" s="10" t="s">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="E122" s="13"/>
     </row>
     <row r="123" spans="1:5" ht="18" customHeight="1">
-      <c r="A123" s="33" t="s">
-        <v>422</v>
-      </c>
-      <c r="B123" s="36" t="s">
-        <v>423</v>
+      <c r="A123" s="36" t="s">
+        <v>399</v>
+      </c>
+      <c r="B123" s="33" t="s">
+        <v>400</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="E123" s="13"/>
     </row>
     <row r="124" spans="1:5" ht="18" customHeight="1">
       <c r="A124" s="35"/>
-      <c r="B124" s="37"/>
+      <c r="B124" s="38"/>
       <c r="C124" s="20" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="E124" s="13"/>
     </row>
     <row r="125" spans="1:5" ht="18" customHeight="1">
       <c r="A125" s="10" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>427</v>
+        <v>404</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="E125" s="13"/>
     </row>
     <row r="126" spans="1:5" ht="18" customHeight="1">
-      <c r="A126" s="33" t="s">
-        <v>428</v>
-      </c>
-      <c r="B126" s="36" t="s">
-        <v>429</v>
+      <c r="A126" s="36" t="s">
+        <v>405</v>
+      </c>
+      <c r="B126" s="33" t="s">
+        <v>406</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>430</v>
+        <v>407</v>
       </c>
       <c r="E126" s="13"/>
     </row>
     <row r="127" spans="1:5" ht="18" customHeight="1">
       <c r="A127" s="34"/>
-      <c r="B127" s="38"/>
+      <c r="B127" s="37"/>
       <c r="C127" s="15" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="E127" s="13"/>
     </row>
     <row r="128" spans="1:5" ht="18" customHeight="1">
       <c r="A128" s="35"/>
-      <c r="B128" s="37"/>
+      <c r="B128" s="38"/>
       <c r="C128" s="17" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="E128" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:E128" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="51">
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A109:A112"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B86:B92"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B104:B108"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B68:B73"/>
+    <mergeCell ref="B109:B112"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="A97:A99"/>
+    <mergeCell ref="A68:A73"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B4:B18"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B58:B67"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="A58:A67"/>
+    <mergeCell ref="B126:B128"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="A126:A128"/>
+    <mergeCell ref="A86:A92"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="B74:B80"/>
+    <mergeCell ref="A100:A103"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A37:A40"/>
     <mergeCell ref="A104:A108"/>
@@ -6801,41 +7293,6 @@
     <mergeCell ref="A43:A47"/>
     <mergeCell ref="B100:B103"/>
     <mergeCell ref="A4:A18"/>
-    <mergeCell ref="B126:B128"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="A126:A128"/>
-    <mergeCell ref="A86:A92"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="B97:B99"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="B74:B80"/>
-    <mergeCell ref="A100:A103"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="B4:B18"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B58:B67"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="A58:A67"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A109:A112"/>
-    <mergeCell ref="B81:B85"/>
-    <mergeCell ref="B86:B92"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B104:B108"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B68:B73"/>
-    <mergeCell ref="B109:B112"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A97:A99"/>
-    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
